--- a/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R627a36f7221040db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd4683d4fbda74bea"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd4683d4fbda74bea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5da590564114339"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra5da590564114339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R607033b9b99d4a3f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R607033b9b99d4a3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref8efd80657d4871"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref8efd80657d4871"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R874e2db50f1b4348"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R874e2db50f1b4348"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9c94ae1a43bc4cbc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PageSetupHeaderFooterVariants/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9c94ae1a43bc4cbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e5a55f473b34332"/>
   </x:sheets>
 </x:workbook>
 </file>
